--- a/data/S1975_76_FINAL.xlsx
+++ b/data/S1975_76_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +82,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,12 +100,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21997,7 +22015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22041,6 +22059,59 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1975_76_0074 'TJ Sokol Bernartice' prev→CLUB_S1974_75_0197 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1975_76_0477 'TJ Sokol Ostrava Poruba' prev→CLUB_S1974_75_0095 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1975_76_0548 'Tatran Bystřice pod Hostýnem' prev→CLUB_S1974_75_0424 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0013</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1975_76_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1975_76_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -53767,6 +53838,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0074</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0074 'TJ Sokol Bernartice' prev→CLUB_S1974_75_0197 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0477</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0477 'TJ Sokol Ostrava Poruba' prev→CLUB_S1974_75_0095 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0548</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0548 'Tatran Bystřice pod Hostýnem' prev→CLUB_S1974_75_0424 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0013</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1975_76_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1975_76_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1975_76_FINAL.xlsx
+++ b/data/S1975_76_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5815,11 +5815,7 @@
           <t>CLUB_S1975_76_0319</t>
         </is>
       </c>
-      <c r="R47" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0015</t>
-        </is>
-      </c>
+      <c r="R47" s="3" t="n"/>
       <c r="S47" s="3" t="n"/>
       <c r="T47" s="3" t="n"/>
       <c r="U47" s="3" t="n"/>
@@ -5864,11 +5860,7 @@
           <t>CLUB_S1975_76_0320</t>
         </is>
       </c>
-      <c r="R48" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0015</t>
-        </is>
-      </c>
+      <c r="R48" s="3" t="n"/>
       <c r="S48" s="3" t="n"/>
       <c r="T48" s="3" t="n"/>
       <c r="U48" s="3" t="n"/>
@@ -6007,11 +5999,7 @@
           <t>CLUB_S1975_76_0323</t>
         </is>
       </c>
-      <c r="R51" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0015</t>
-        </is>
-      </c>
+      <c r="R51" s="3" t="n"/>
       <c r="S51" s="3" t="n"/>
       <c r="T51" s="3" t="n"/>
       <c r="U51" s="3" t="n"/>
@@ -22015,7 +22003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22065,7 +22053,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1975_76_0074 'TJ Sokol Bernartice' prev→CLUB_S1974_75_0197 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22077,7 +22065,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1975_76_0477 'TJ Sokol Ostrava Poruba' prev→CLUB_S1974_75_0095 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22089,7 +22077,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1975_76_0548 'Tatran Bystřice pod Hostýnem' prev→CLUB_S1974_75_0424 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22099,17 +22087,576 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1975_76_0013</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1975_76_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1975_76_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1974_75_0197 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0095 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Válcovny plechu Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0515 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0370 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0424 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0405 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -30515,12 +31062,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -30819,12 +31366,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -31039,12 +31586,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -31207,12 +31754,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -31249,12 +31796,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -32020,12 +32567,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -32062,12 +32609,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -32230,12 +32777,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -32319,12 +32866,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou.</t>
+          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou. || TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Kaučuk Kralupy</t>
+          <t>Kralupy nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -32361,12 +32908,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -32764,12 +33311,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -32806,12 +33353,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -33063,12 +33610,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -33236,12 +33783,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -33624,12 +34171,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -33839,12 +34386,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -38004,12 +38551,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38607,12 +39154,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -39104,12 +39651,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -40659,12 +41206,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -43624,19 +44171,14 @@
           <t>Ústí nad Labem</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0015</t>
-        </is>
-      </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -43671,19 +44213,14 @@
           <t>Ústí nad Labem</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0015</t>
-        </is>
-      </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -43807,19 +44344,14 @@
           <t>Ústí nad Labem</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>CLUB_S1974_75_0015</t>
-        </is>
-      </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -44370,12 +44902,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -45569,12 +46101,12 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -47619,12 +48151,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Nářadí Zborovice</t>
         </is>
       </c>
     </row>
@@ -47666,12 +48198,12 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -49678,12 +50210,12 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>Bystřice</t>
+          <t>Bystřice pod Hostýnem</t>
         </is>
       </c>
     </row>
@@ -49725,12 +50257,12 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -50232,12 +50764,12 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -50625,12 +51157,12 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -50788,12 +51320,12 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm.</t>
+          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm. || TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>MEZ Frenštát</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -51648,12 +52180,12 @@
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek. || TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>VP Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -52921,12 +53453,12 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ Válcovny plechu Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Válcovny plechu** = pobocka Třinecké železárny. Patterns: VP -&gt; Válcovny plechu Frýdek-Místek. city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ Válcovny plechu Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Válcovny plechu** = pobocka Třinecké železárny. Patterns: VP -&gt; Válcovny plechu Frýdek-Místek. city Frýdek-Místek. || TBD: city 'Válcovny plechu Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>Válcovny plechu Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -53084,12 +53616,12 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Krizovany nad Dudváhom = TJ Družstevník Krizovany nad Dudváhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj (okres Trnava). city Krizovany nad Dudváhom.</t>
+          <t>Krizovany nad Dudváhom = TJ Družstevník Krizovany nad Dudváhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj (okres Trnava). city Krizovany nad Dudváhom. || TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>Družstevník Krizovany nad Dudváhom</t>
+          <t>Krizovany nad Dudváhom</t>
         </is>
       </c>
     </row>
@@ -53126,12 +53658,12 @@
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>Nitra = TJ Slávia VŠP Nitra (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. **VŠP** = Vysoká škola pedagogická (dnes Univerzita Konštantína Filozofa, UKF Nitra). city Nitra.</t>
+          <t>Nitra = TJ Slávia VŠP Nitra (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. **VŠP** = Vysoká škola pedagogická (dnes Univerzita Konštantína Filozofa, UKF Nitra). city Nitra. || TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>Slávia VŠP Nitra</t>
+          <t>VŠP Nitra</t>
         </is>
       </c>
     </row>
@@ -53168,12 +53700,12 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>Bánovce nad Bebravou = TJ Slávia Zornica Bánovce nad Bebravou (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. **Zornica** = obuvnicky podnik (vyrobce obuvi Zornica). city Bánovce nad Bebravou.</t>
+          <t>Bánovce nad Bebravou = TJ Slávia Zornica Bánovce nad Bebravou (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. **Zornica** = obuvnicky podnik (vyrobce obuvi Zornica). city Bánovce nad Bebravou. || TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>Slávia Zornica Bánovce nad Bebravou</t>
+          <t>Bánovce nad Bebravou</t>
         </is>
       </c>
     </row>
@@ -53420,12 +53952,12 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0515 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0515 (strong, jméno+město; verifikovat) [fix_continuity] || TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>Technické služby Děčín</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
@@ -53844,11 +54376,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -53893,21 +54425,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0074</t>
+          <t>CLUB_S1975_76_0010</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0074 'TJ Sokol Bernartice' prev→CLUB_S1974_75_0197 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -53915,21 +54445,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0477</t>
+          <t>CLUB_S1975_76_0017</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0477 'TJ Sokol Ostrava Poruba' prev→CLUB_S1974_75_0095 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -53937,21 +54465,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0548</t>
+          <t>CLUB_S1975_76_0022</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0548 'Tatran Bystřice pod Hostýnem' prev→CLUB_S1974_75_0424 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -53959,24 +54485,962 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1975_76_0013</t>
+          <t>CLUB_S1975_76_0026</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1975_76_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1975_76_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0027</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0045</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0046</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0050</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0052</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0053</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0062</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0063</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0069</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0073</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0074</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1974_75_0197 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0082</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0087</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0186</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0200</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0200</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0211</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0247</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0319</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0319</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0320</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0320</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0323</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0323</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0337</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0364</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0402</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0410</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0411</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0447</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0451</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0458</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0459</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0470</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0477</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0095 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0480</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0484</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0504</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0533</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Válcovny plechu Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0538</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0539</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0540</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0546</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0515 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0546</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0547</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0370 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0548</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0424 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S1975_76_0549</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0405 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1975_76_FINAL.xlsx
+++ b/data/S1975_76_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22003,7 +22003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22053,7 +22053,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22065,7 +22065,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22077,7 +22077,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22089,7 +22089,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22101,7 +22101,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22113,7 +22113,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -22125,7 +22125,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22137,7 +22137,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22149,7 +22149,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22161,7 +22161,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1974_75_0197 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -22173,7 +22173,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -22185,7 +22185,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -22197,7 +22197,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22209,7 +22209,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -22221,7 +22221,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1974_75_0197 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -22233,7 +22233,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -22245,7 +22245,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -22257,7 +22257,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -22269,7 +22269,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -22281,7 +22281,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -22293,7 +22293,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -22305,7 +22305,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -22317,7 +22317,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -22329,7 +22329,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -22341,7 +22341,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -22353,7 +22353,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -22365,7 +22365,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -22377,7 +22377,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -22389,7 +22389,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0095 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -22401,7 +22401,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -22413,7 +22413,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22425,7 +22425,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Válcovny plechu Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -22437,7 +22437,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -22449,7 +22449,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -22461,7 +22461,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -22473,7 +22473,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0515 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -22485,7 +22485,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -22497,7 +22497,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0370 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -22509,7 +22509,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0095 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0424 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -22521,142 +22521,10 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0405 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Válcovny plechu Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0515 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0370 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0424 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0405 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -22673,7 +22541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22732,6 +22600,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22774,6 +22647,11 @@
           <t>12 týmů: základ → finále (1-6) + o udržení (7-12). Mistr: SONP Kladno.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22821,6 +22699,11 @@
           <t>Sedmizápasová série Gottwaldov – Zvolen 4:3. 1., 2. a 5. utkání doma, 7. utkání na neutrálním ledě v Praze Edenu. Při remíze prodloužení/nájezdy dle PDF.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22863,6 +22746,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK). Kvalifikace o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22905,6 +22793,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22947,6 +22840,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22989,6 +22887,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23031,6 +22934,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23073,6 +22981,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23115,6 +23028,11 @@
           <t>II.ČNHL: 3 skupiny po 8. Nově založená soutěž.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23157,6 +23075,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23199,6 +23122,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23241,6 +23169,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23330,6 +23263,11 @@
           <t>Divize: 6 skupin CZ (A-F) + SVK západ/východ + kvalifikace.</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23372,6 +23310,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23414,6 +23357,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23456,6 +23404,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23498,6 +23451,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -23540,6 +23498,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -23582,6 +23545,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0023</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -23629,6 +23597,11 @@
           <t>Finále slovenské divize: TJ TS Topoľčany – TJ Lokomotíva Bane Spišská Nová Ves; skóre v PDF neuvedeno.</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -23676,6 +23649,11 @@
           <t>PDF vede blok jako kvalifikaci o divizi; raw/prepared používají starší label "postup do II.ligy". Ve workbooku je použitá metodika podle PDF.</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -23718,6 +23696,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0028</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23844,6 +23827,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0034</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -23886,6 +23874,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0035</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -23928,6 +23921,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0036</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -23970,6 +23968,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0037</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -24096,6 +24099,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0036</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -24138,6 +24146,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0037</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -24264,6 +24277,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0038</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -24521,6 +24539,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0049</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -24563,6 +24586,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0050</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -24605,6 +24633,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0051</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -24647,6 +24680,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0052</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -24689,6 +24727,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0053</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -24825,6 +24868,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0055</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -24867,6 +24915,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0056</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -24909,6 +24962,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0060</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -24951,6 +25009,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0061</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -24993,6 +25056,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0062</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -25035,6 +25103,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0063</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -25082,6 +25155,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0065</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -25124,6 +25202,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0066</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -25166,6 +25249,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0067</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -25250,6 +25338,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0069</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -25292,6 +25385,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0070</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -25334,6 +25432,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0071</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -25418,6 +25521,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0073</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -25885,6 +25993,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0087</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -25927,6 +26040,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0088</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -25969,6 +26087,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0089</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -26011,6 +26134,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0090</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -26053,6 +26181,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0091</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -26310,6 +26443,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0100</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -26352,6 +26490,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0101</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -26436,6 +26579,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0103</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -26478,6 +26626,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0104</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -26520,6 +26673,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0105</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -26656,6 +26814,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0103</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -26698,6 +26861,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0104</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -26740,6 +26908,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0109</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -26782,6 +26955,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0110</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -26822,6 +27000,11 @@
       <c r="J97" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1974_75_0111</t>
         </is>
       </c>
     </row>
@@ -31062,12 +31245,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -31586,12 +31769,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -31754,12 +31937,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -32567,12 +32750,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -32609,12 +32792,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -39154,12 +39337,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -46101,12 +46284,12 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -48151,12 +48334,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>Nářadí Zborovice</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -48198,12 +48381,12 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -50210,12 +50393,12 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>Bystřice pod Hostýnem</t>
+          <t>Bystřice u Benešova</t>
         </is>
       </c>
     </row>
@@ -51157,12 +51340,12 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -54376,7 +54559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -54430,12 +54613,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0010</t>
+          <t>CLUB_S1975_76_0017</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54450,12 +54633,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0017</t>
+          <t>CLUB_S1975_76_0027</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54470,12 +54653,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0022</t>
+          <t>CLUB_S1975_76_0050</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54490,12 +54673,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0026</t>
+          <t>CLUB_S1975_76_0052</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54510,12 +54693,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0027</t>
+          <t>CLUB_S1975_76_0053</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54530,12 +54713,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0045</t>
+          <t>CLUB_S1975_76_0062</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54550,12 +54733,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0046</t>
+          <t>CLUB_S1975_76_0063</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54570,12 +54753,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0050</t>
+          <t>CLUB_S1975_76_0069</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54590,12 +54773,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0052</t>
+          <t>CLUB_S1975_76_0073</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54610,12 +54793,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0053</t>
+          <t>CLUB_S1975_76_0074</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1974_75_0197 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -54630,12 +54813,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0062</t>
+          <t>CLUB_S1975_76_0082</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54650,12 +54833,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0063</t>
+          <t>CLUB_S1975_76_0087</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54670,12 +54853,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0069</t>
+          <t>CLUB_S1975_76_0186</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54690,12 +54873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0073</t>
+          <t>CLUB_S1975_76_0200</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54710,12 +54893,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0074</t>
+          <t>CLUB_S1975_76_0211</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1974_75_0197 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54730,12 +54913,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0082</t>
+          <t>CLUB_S1975_76_0247</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54750,12 +54933,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0087</t>
+          <t>CLUB_S1975_76_0319</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54770,12 +54953,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0186</t>
+          <t>CLUB_S1975_76_0319</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54790,12 +54973,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0200</t>
+          <t>CLUB_S1975_76_0320</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54810,12 +54993,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0200</t>
+          <t>CLUB_S1975_76_0320</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54830,12 +55013,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0211</t>
+          <t>CLUB_S1975_76_0323</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54850,12 +55033,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0247</t>
+          <t>CLUB_S1975_76_0323</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54870,12 +55053,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0319</t>
+          <t>CLUB_S1975_76_0337</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54890,12 +55073,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0319</t>
+          <t>CLUB_S1975_76_0402</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -54910,12 +55093,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0320</t>
+          <t>CLUB_S1975_76_0447</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -54930,12 +55113,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0320</t>
+          <t>CLUB_S1975_76_0451</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -54950,12 +55133,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0323</t>
+          <t>CLUB_S1975_76_0459</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54970,12 +55153,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0323</t>
+          <t>CLUB_S1975_76_0470</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -54990,12 +55173,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0337</t>
+          <t>CLUB_S1975_76_0477</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0095 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55010,12 +55193,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0364</t>
+          <t>CLUB_S1975_76_0484</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55030,12 +55213,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0402</t>
+          <t>CLUB_S1975_76_0504</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55050,12 +55233,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0410</t>
+          <t>CLUB_S1975_76_0533</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Válcovny plechu Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55070,12 +55253,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0411</t>
+          <t>CLUB_S1975_76_0538</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55090,12 +55273,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0447</t>
+          <t>CLUB_S1975_76_0539</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55110,12 +55293,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0451</t>
+          <t>CLUB_S1975_76_0540</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55130,12 +55313,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0458</t>
+          <t>CLUB_S1975_76_0546</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0515 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55150,12 +55333,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0459</t>
+          <t>CLUB_S1975_76_0546</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55170,12 +55353,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0470</t>
+          <t>CLUB_S1975_76_0547</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0370 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55190,12 +55373,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0477</t>
+          <t>CLUB_S1975_76_0548</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0095 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0424 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55210,237 +55393,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0480</t>
+          <t>CLUB_S1975_76_0549</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0484</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0504</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0533</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Válcovny plechu Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0538</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0539</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0540</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slávia Zornica Bánovce nad Bebravou' → 'Bánovce nad Bebravou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0546</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0515 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0546</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0547</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0370 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0548</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0424 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CLUB_S1975_76_0549</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1974_75_0405 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F52"/>
+  <autoFilter ref="A1:F41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1975_76_FINAL.xlsx
+++ b/data/S1975_76_FINAL.xlsx
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M5" t="n">
         <v>30</v>
@@ -848,7 +848,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>

--- a/data/S1975_76_FINAL.xlsx
+++ b/data/S1975_76_FINAL.xlsx
@@ -30009,7 +30009,7 @@
         <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M21" t="n">
         <v>45</v>
@@ -60565,7 +60565,7 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M42" t="n">
         <v>13</v>

--- a/data/S1975_76_FINAL.xlsx
+++ b/data/S1975_76_FINAL.xlsx
@@ -22541,7 +22541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22603,6 +22603,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1975_76_FINAL.xlsx
+++ b/data/S1975_76_FINAL.xlsx
@@ -22887,6 +22887,16 @@
           <t>NODE_S1975_76_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22901,6 +22911,14 @@
         <is>
           <t>NODE_S1974_75_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -22934,6 +22952,8 @@
           <t>NODE_S1975_76_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22948,6 +22968,14 @@
         <is>
           <t>NODE_S1974_75_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -22981,6 +23009,8 @@
           <t>NODE_S1975_76_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22995,6 +23025,14 @@
         <is>
           <t>NODE_S1974_75_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>7.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -23592,6 +23630,8 @@
           <t>NODE_S1975_76_0015</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23611,6 +23651,14 @@
         <is>
           <t>NODE_S1974_75_0024</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -24057,6 +24105,8 @@
           <t>NODE_S1975_76_0028</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24066,6 +24116,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -24277,6 +24335,8 @@
           <t>NODE_S1975_76_0028</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24291,6 +24351,14 @@
         <is>
           <t>NODE_S1974_75_0038</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -25197,6 +25265,12 @@
           <t>REG_SEC</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0064</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25216,6 +25290,14 @@
         <is>
           <t>NODE_S1974_75_0066</t>
         </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -25479,6 +25561,8 @@
           <t>NODE_S1975_76_0058</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25488,6 +25572,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -25694,6 +25786,8 @@
           <t>NODE_S1975_76_0065</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25703,6 +25797,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -25904,6 +26006,8 @@
           <t>NODE_S1975_76_0066</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25913,6 +26017,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -26181,6 +26293,8 @@
           <t>NODE_S1975_76_0076</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26195,6 +26309,14 @@
         <is>
           <t>NODE_S1974_75_0091</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -26715,11 +26837,8 @@
           <t>REG_SVM</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>NODE_S1975_76_0025</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26734,6 +26853,14 @@
         <is>
           <t>finále (kvalifikace o KP)</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="92">

--- a/data/S1975_76_FINAL.xlsx
+++ b/data/S1975_76_FINAL.xlsx
@@ -1735,6 +1735,11 @@
           <t>SONP Kladno</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F18" t="n">
         <v>32</v>
       </c>
@@ -22952,8 +22957,6 @@
           <t>NODE_S1975_76_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23009,8 +23012,6 @@
           <t>NODE_S1975_76_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23630,8 +23631,6 @@
           <t>NODE_S1975_76_0015</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24105,8 +24104,6 @@
           <t>NODE_S1975_76_0028</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24335,8 +24332,6 @@
           <t>NODE_S1975_76_0028</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25270,7 +25265,6 @@
           <t>NODE_S1975_76_0064</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25561,8 +25555,6 @@
           <t>NODE_S1975_76_0058</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25786,8 +25778,6 @@
           <t>NODE_S1975_76_0065</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26006,8 +25996,6 @@
           <t>NODE_S1975_76_0066</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26293,8 +26281,6 @@
           <t>NODE_S1975_76_0076</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26837,8 +26823,6 @@
           <t>REG_SVM</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -54418,7 +54402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54682,6 +54666,18 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>Finále slovenské divize je doloženo dvojicí Topoľčany – Spišská Nová Ves, ale bez zveřejněných výsledků.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SONP Kladno</t>
         </is>
       </c>
     </row>

--- a/data/S1975_76_FINAL.xlsx
+++ b/data/S1975_76_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22008,7 +22008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22530,6 +22530,23 @@
         </is>
       </c>
       <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0092</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: '30_Severomoravský finále (kvalifikace o KP)'</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -54692,7 +54709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -55535,8 +55552,28 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0092</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: '30_Severomoravský finále (kvalifikace o KP)'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F41"/>
+  <autoFilter ref="A1:F42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
